--- a/results_v3/tables/table6_ood_robustness.xlsx
+++ b/results_v3/tables/table6_ood_robustness.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,136 +540,247 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.00±0.00</t>
+          <t>1.00±0.00 (drop -3.1%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95±0.00</t>
+          <t>0.95±0.00 (drop 2.5%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.97±0.00</t>
+          <t>0.97±0.00 (drop 0.2%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>0.00±0.00 (drop 100.0%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.95±0.00</t>
+          <t>0.95±0.00 (drop 1.9%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>POMCP (known model)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.33±0.05</t>
+          <t>0.92±0.01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.35±0.07 (drop -7.0%)</t>
+          <t>0.98±0.00 (drop -6.4%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33±0.03 (drop -0.6%)</t>
+          <t>0.88±0.01 (drop 4.6%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.06±0.04 (drop 81.0%)</t>
+          <t>0.87±0.00 (drop 5.9%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.34±0.07 (drop -2.7%)</t>
+          <t>0.31±0.03 (drop 65.8%)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.33±0.05 (drop -1.0%)</t>
+          <t>0.90±0.01 (drop 1.9%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>DQN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.33±0.03</t>
+          <t>0.33±0.05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.32±0.04 (drop 5.3%)</t>
+          <t>0.35±0.07 (drop -7.0%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.26±0.04 (drop 21.2%)</t>
+          <t>0.33±0.03 (drop -0.6%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.04±0.02 (drop 88.0%)</t>
+          <t>0.06±0.04 (drop 81.0%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.30±0.04 (drop 9.5%)</t>
+          <t>0.34±0.07 (drop -2.7%)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.30±0.03 (drop 10.6%)</t>
+          <t>0.33±0.05 (drop -1.0%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.33±0.03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.32±0.04 (drop 5.3%)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.26±0.04 (drop 21.2%)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.04±0.02 (drop 88.0%)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.30±0.04 (drop 9.5%)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.30±0.03 (drop 10.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DQN-GRU (memory)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.47±0.04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.48±0.04 (drop -2.1%)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.45±0.03 (drop 3.2%)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.08±0.04 (drop 83.3%)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.45±0.04 (drop 3.8%)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.47±0.03 (drop 0.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PPO-Stack (memory)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.36±0.07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.36±0.08 (drop -0.1%)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.34±0.07 (drop 4.4%)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.06±0.02 (drop 84.6%)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.34±0.08 (drop 4.7%)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.35±0.07 (drop 1.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>MuZero (ours)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0.68±0.03</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0.74±0.04 (drop -9.4%)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.65±0.04 (drop 4.4%)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>0.18±0.02 (drop 73.2%)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>0.69±0.04 (drop -1.5%)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>0.66±0.02 (drop 1.5%)</t>
         </is>
